--- a/Sharedpointrequest/CurrentlyRunningItem.xlsx
+++ b/Sharedpointrequest/CurrentlyRunningItem.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA Folders\Migration\Fusion_TAXLineUpdate\content\Sharedpointrequest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E035B2-9EE0-4087-99A5-8753585B79F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9489030A-F5F3-4C49-914B-DE26BF4AE0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,10 +30,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
